--- a/sheets/customers.xlsx
+++ b/sheets/customers.xlsx
@@ -466,7 +466,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -486,7 +486,7 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
